--- a/public/songlist.xlsx
+++ b/public/songlist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Frontend\Vue\songlist-multi\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE6AAF1-F471-476B-A6F7-2B07FA52F9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A981CDB-B11C-4553-9FAA-E1FA561F5F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="5415" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="1365" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="songlist" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
   <si>
     <t>歌名</t>
   </si>
@@ -76,9 +76,6 @@
     <t>歌单标题</t>
   </si>
   <si>
-    <t>XX的歌单</t>
-  </si>
-  <si>
     <t>浏览器标签页与侧栏标题</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>窄屏背景，支持网络地址</t>
   </si>
   <si>
-    <t>可以放邮箱里一并发给我</t>
-  </si>
-  <si>
     <t>背景图-宽屏</t>
   </si>
   <si>
@@ -124,126 +118,159 @@
     <t>占位符 {title} {singer} {lang} {tags}</t>
   </si>
   <si>
-    <t>看不明白可以不改</t>
+    <t>甲乙丙丁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李佳薇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流行；苦情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三十八年夏至</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同簪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小时姑娘、HITA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国风；甜歌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>舰长</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>星空剪影</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝心羽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流行；甜歌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>太陽と向日葵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Show</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lenka</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>眉间雪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HITA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国风；苦情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歌切</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>不会填可以直接发给我文件</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>16进制色值，其他配色会自动计算</t>
+  </si>
+  <si>
+    <t>看不懂可以不改</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>主播UID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不知道如何填写的话空着，我会去拿</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>直播间ID</t>
+  </si>
+  <si>
+    <t>直播间</t>
+  </si>
+  <si>
+    <t>由直播间ID派生,此处仅备份</t>
+  </si>
+  <si>
+    <t>模板外字段,仅供备份，不要修改</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>favicon</t>
+  </si>
+  <si>
+    <t>XXX的歌单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不知道怎么填就空着，我会去取</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>点击卡片复制点歌口令,回到直播间粘贴即可点歌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://i0.hdslb.com/bfs/face/f4d205b7279bd85570cdf5a2246c9da1248fe1db.jpg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>16进制色值，其他配色会自动计算不填的话就是默认的蓝色</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>直播间ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>甲乙丙丁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李佳薇</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流行；苦情</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>第三十八年夏至</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同簪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>小时姑娘、HITA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>国风；甜歌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>舰长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>星空剪影</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝心羽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流行；甜歌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>太陽と向日葵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flower</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日文</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Show</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lenka</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>英文</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>眉间雪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HITA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>国风；苦情</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>歌切</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
+  </si>
+  <si>
+    <t>3783846</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://live.bilibili.com/3783846</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>23598218</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>//i0.hdslb.com/bfs/face/f4d205b7279bd85570cdf5a2246c9da1248fe1db.jpg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -251,7 +278,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -283,11 +310,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -313,11 +347,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -326,11 +359,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -638,24 +672,24 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -663,13 +697,13 @@
     </row>
     <row r="3" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -680,33 +714,33 @@
     </row>
     <row r="4" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
@@ -714,27 +748,27 @@
     </row>
     <row r="6" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -742,16 +776,16 @@
     </row>
     <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -995,132 +1029,187 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="71.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="59" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="85.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="59" style="8" customWidth="1"/>
+    <col min="4" max="4" width="44.7109375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="B6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="D6" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
+      <c r="D8" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{9912B52C-EB79-4172-893C-AE2B77864B02}"/>
+    <hyperlink ref="B11" r:id="rId1" xr:uid="{84845B8B-6708-4D72-903E-61F959D14037}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
